--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.53367932473465</v>
+        <v>2.03672289026938</v>
       </c>
       <c r="D2" t="n">
-        <v>12.51052519872072</v>
+        <v>2.032960344792117</v>
       </c>
       <c r="E2" t="n">
-        <v>3.959661737626778</v>
+        <v>0.6434450323643515</v>
       </c>
       <c r="F2" t="n">
-        <v>3.906680266863999</v>
+        <v>0.6348355433653999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.67176798296931</v>
+        <v>3.359162297232512</v>
       </c>
       <c r="D3" t="n">
-        <v>20.70019337046828</v>
+        <v>3.363781422701095</v>
       </c>
       <c r="E3" t="n">
-        <v>3.959661737626778</v>
+        <v>0.6434450323643515</v>
       </c>
       <c r="F3" t="n">
-        <v>3.906680266863999</v>
+        <v>0.6348355433653999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.17260106872309</v>
+        <v>3.440547673667503</v>
       </c>
       <c r="D4" t="n">
-        <v>20.89216224382523</v>
+        <v>3.3949763646216</v>
       </c>
       <c r="E4" t="n">
-        <v>3.959661737626778</v>
+        <v>0.6434450323643515</v>
       </c>
       <c r="F4" t="n">
-        <v>3.906680266863999</v>
+        <v>0.6348355433653999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
